--- a/datos-referencia/reservas_credito.xlsx
+++ b/datos-referencia/reservas_credito.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="65">
   <si>
     <t>numero_reserva</t>
   </si>
@@ -109,6 +109,78 @@
     <t>Iberdrola Clientes SAU</t>
   </si>
   <si>
+    <t>2027-04-06</t>
+  </si>
+  <si>
+    <t>2027-04-11</t>
+  </si>
+  <si>
+    <t>2027-03-17</t>
+  </si>
+  <si>
+    <t>2027-04-21</t>
+  </si>
+  <si>
+    <t>2027-03-07</t>
+  </si>
+  <si>
+    <t>2027-02-20</t>
+  </si>
+  <si>
+    <t>2027-04-16</t>
+  </si>
+  <si>
+    <t>2027-03-27</t>
+  </si>
+  <si>
+    <t>2027-02-10</t>
+  </si>
+  <si>
+    <t>2027-04-26</t>
+  </si>
+  <si>
+    <t>2027-01-31</t>
+  </si>
+  <si>
+    <t>2027-01-21</t>
+  </si>
+  <si>
+    <t>2027-04-09</t>
+  </si>
+  <si>
+    <t>2027-04-13</t>
+  </si>
+  <si>
+    <t>2027-03-20</t>
+  </si>
+  <si>
+    <t>2027-04-23</t>
+  </si>
+  <si>
+    <t>2027-03-10</t>
+  </si>
+  <si>
+    <t>2027-02-25</t>
+  </si>
+  <si>
+    <t>2027-04-18</t>
+  </si>
+  <si>
+    <t>2027-03-29</t>
+  </si>
+  <si>
+    <t>2027-02-13</t>
+  </si>
+  <si>
+    <t>2027-04-28</t>
+  </si>
+  <si>
+    <t>2027-02-02</t>
+  </si>
+  <si>
+    <t>2027-01-24</t>
+  </si>
+  <si>
     <t>PENDIENTE_FACTURA</t>
   </si>
   <si>
@@ -116,25 +188,35 @@
   </si>
   <si>
     <t>COBRADO</t>
+  </si>
+  <si>
+    <t>2027-03-22</t>
+  </si>
+  <si>
+    <t>2027-03-12</t>
+  </si>
+  <si>
+    <t>2027-02-27</t>
+  </si>
+  <si>
+    <t>2027-04-01</t>
+  </si>
+  <si>
+    <t>2027-02-15</t>
+  </si>
+  <si>
+    <t>2027-02-05</t>
+  </si>
+  <si>
+    <t>2027-01-26</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
-  </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -150,7 +232,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -158,31 +240,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -481,37 +544,37 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
     </row>
@@ -522,11 +585,11 @@
       <c r="B2" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="2">
-        <v>46148</v>
-      </c>
-      <c r="D2" s="2">
-        <v>46151</v>
+      <c r="C2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" t="s">
+        <v>43</v>
       </c>
       <c r="E2">
         <v>4</v>
@@ -544,7 +607,7 @@
         <v>3200</v>
       </c>
       <c r="J2" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -554,11 +617,11 @@
       <c r="B3" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="2">
-        <v>46153</v>
-      </c>
-      <c r="D3" s="2">
-        <v>46155</v>
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" t="s">
+        <v>44</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -576,7 +639,7 @@
         <v>1600</v>
       </c>
       <c r="J3" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -586,11 +649,11 @@
       <c r="B4" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="2">
-        <v>46128</v>
-      </c>
-      <c r="D4" s="2">
-        <v>46131</v>
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" t="s">
+        <v>45</v>
       </c>
       <c r="E4">
         <v>8</v>
@@ -608,10 +671,10 @@
         <v>6720</v>
       </c>
       <c r="J4" t="s">
-        <v>32</v>
-      </c>
-      <c r="K4" s="2">
-        <v>46133</v>
+        <v>56</v>
+      </c>
+      <c r="K4" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -621,11 +684,11 @@
       <c r="B5" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="2">
-        <v>46163</v>
-      </c>
-      <c r="D5" s="2">
-        <v>46165</v>
+      <c r="C5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" t="s">
+        <v>46</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -643,7 +706,7 @@
         <v>2370</v>
       </c>
       <c r="J5" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -653,11 +716,11 @@
       <c r="B6" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="2">
-        <v>46118</v>
-      </c>
-      <c r="D6" s="2">
-        <v>46121</v>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>47</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -675,10 +738,10 @@
         <v>4000</v>
       </c>
       <c r="J6" t="s">
-        <v>32</v>
-      </c>
-      <c r="K6" s="2">
-        <v>46123</v>
+        <v>56</v>
+      </c>
+      <c r="K6" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -688,11 +751,11 @@
       <c r="B7" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="2">
-        <v>46103</v>
-      </c>
-      <c r="D7" s="2">
-        <v>46108</v>
+      <c r="C7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" t="s">
+        <v>48</v>
       </c>
       <c r="E7">
         <v>12</v>
@@ -710,10 +773,10 @@
         <v>10600</v>
       </c>
       <c r="J7" t="s">
-        <v>32</v>
-      </c>
-      <c r="K7" s="2">
-        <v>46110</v>
+        <v>56</v>
+      </c>
+      <c r="K7" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -723,11 +786,11 @@
       <c r="B8" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="2">
-        <v>46158</v>
-      </c>
-      <c r="D8" s="2">
-        <v>46160</v>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" t="s">
+        <v>49</v>
       </c>
       <c r="E8">
         <v>2</v>
@@ -745,7 +808,7 @@
         <v>1480</v>
       </c>
       <c r="J8" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -755,11 +818,11 @@
       <c r="B9" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="2">
-        <v>46138</v>
-      </c>
-      <c r="D9" s="2">
-        <v>46140</v>
+      <c r="C9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" t="s">
+        <v>50</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -777,10 +840,10 @@
         <v>1480</v>
       </c>
       <c r="J9" t="s">
-        <v>32</v>
-      </c>
-      <c r="K9" s="2">
-        <v>46143</v>
+        <v>56</v>
+      </c>
+      <c r="K9" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -790,11 +853,11 @@
       <c r="B10" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="2">
-        <v>46093</v>
-      </c>
-      <c r="D10" s="2">
-        <v>46096</v>
+      <c r="C10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" t="s">
+        <v>51</v>
       </c>
       <c r="E10">
         <v>6</v>
@@ -812,10 +875,10 @@
         <v>4850</v>
       </c>
       <c r="J10" t="s">
-        <v>32</v>
-      </c>
-      <c r="K10" s="2">
-        <v>46098</v>
+        <v>56</v>
+      </c>
+      <c r="K10" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -825,11 +888,11 @@
       <c r="B11" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="2">
-        <v>46168</v>
-      </c>
-      <c r="D11" s="2">
-        <v>46170</v>
+      <c r="C11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" t="s">
+        <v>52</v>
       </c>
       <c r="E11">
         <v>6</v>
@@ -847,7 +910,7 @@
         <v>4950</v>
       </c>
       <c r="J11" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -857,11 +920,11 @@
       <c r="B12" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="2">
-        <v>46083</v>
-      </c>
-      <c r="D12" s="2">
-        <v>46085</v>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" t="s">
+        <v>53</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -879,10 +942,10 @@
         <v>2300</v>
       </c>
       <c r="J12" t="s">
-        <v>33</v>
-      </c>
-      <c r="K12" s="2">
-        <v>46088</v>
+        <v>57</v>
+      </c>
+      <c r="K12" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -892,11 +955,11 @@
       <c r="B13" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="2">
-        <v>46073</v>
-      </c>
-      <c r="D13" s="2">
-        <v>46076</v>
+      <c r="C13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" t="s">
+        <v>54</v>
       </c>
       <c r="E13">
         <v>4</v>
@@ -914,10 +977,10 @@
         <v>3150</v>
       </c>
       <c r="J13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K13" s="2">
-        <v>46078</v>
+        <v>57</v>
+      </c>
+      <c r="K13" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/datos-referencia/reservas_credito.xlsx
+++ b/datos-referencia/reservas_credito.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="58">
   <si>
     <t>numero_reserva</t>
   </si>
@@ -109,76 +109,76 @@
     <t>Iberdrola Clientes SAU</t>
   </si>
   <si>
-    <t>2027-04-06</t>
-  </si>
-  <si>
-    <t>2027-04-11</t>
-  </si>
-  <si>
-    <t>2027-03-17</t>
-  </si>
-  <si>
-    <t>2027-04-21</t>
-  </si>
-  <si>
-    <t>2027-03-07</t>
-  </si>
-  <si>
-    <t>2027-02-20</t>
-  </si>
-  <si>
-    <t>2027-04-16</t>
-  </si>
-  <si>
-    <t>2027-03-27</t>
-  </si>
-  <si>
-    <t>2027-02-10</t>
-  </si>
-  <si>
-    <t>2027-04-26</t>
-  </si>
-  <si>
-    <t>2027-01-31</t>
-  </si>
-  <si>
-    <t>2027-01-21</t>
-  </si>
-  <si>
-    <t>2027-04-09</t>
-  </si>
-  <si>
-    <t>2027-04-13</t>
-  </si>
-  <si>
-    <t>2027-03-20</t>
-  </si>
-  <si>
-    <t>2027-04-23</t>
-  </si>
-  <si>
-    <t>2027-03-10</t>
-  </si>
-  <si>
-    <t>2027-02-25</t>
-  </si>
-  <si>
-    <t>2027-04-18</t>
-  </si>
-  <si>
-    <t>2027-03-29</t>
-  </si>
-  <si>
-    <t>2027-02-13</t>
-  </si>
-  <si>
-    <t>2027-04-28</t>
-  </si>
-  <si>
-    <t>2027-02-02</t>
-  </si>
-  <si>
-    <t>2027-01-24</t>
+    <t>2026-05-12</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-04-22</t>
+  </si>
+  <si>
+    <t>2026-04-21</t>
+  </si>
+  <si>
+    <t>2026-03-07</t>
+  </si>
+  <si>
+    <t>2026-02-20</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>2026-02-10</t>
+  </si>
+  <si>
+    <t>2026-04-26</t>
+  </si>
+  <si>
+    <t>2026-01-31</t>
+  </si>
+  <si>
+    <t>2026-01-21</t>
+  </si>
+  <si>
+    <t>2026-05-15</t>
+  </si>
+  <si>
+    <t>2026-05-20</t>
+  </si>
+  <si>
+    <t>2026-04-25</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>2026-03-10</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-04-18</t>
+  </si>
+  <si>
+    <t>2026-03-29</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>2026-04-28</t>
+  </si>
+  <si>
+    <t>2026-02-02</t>
+  </si>
+  <si>
+    <t>2026-01-24</t>
   </si>
   <si>
     <t>PENDIENTE_FACTURA</t>
@@ -188,27 +188,6 @@
   </si>
   <si>
     <t>COBRADO</t>
-  </si>
-  <si>
-    <t>2027-03-22</t>
-  </si>
-  <si>
-    <t>2027-03-12</t>
-  </si>
-  <si>
-    <t>2027-02-27</t>
-  </si>
-  <si>
-    <t>2027-04-01</t>
-  </si>
-  <si>
-    <t>2027-02-15</t>
-  </si>
-  <si>
-    <t>2027-02-05</t>
-  </si>
-  <si>
-    <t>2027-01-26</t>
   </si>
 </sst>
 </file>
@@ -674,7 +653,7 @@
         <v>56</v>
       </c>
       <c r="K4" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -741,7 +720,7 @@
         <v>56</v>
       </c>
       <c r="K6" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -776,7 +755,7 @@
         <v>56</v>
       </c>
       <c r="K7" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -843,7 +822,7 @@
         <v>56</v>
       </c>
       <c r="K9" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -878,7 +857,7 @@
         <v>56</v>
       </c>
       <c r="K10" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -945,7 +924,7 @@
         <v>57</v>
       </c>
       <c r="K12" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -980,7 +959,7 @@
         <v>57</v>
       </c>
       <c r="K13" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/datos-referencia/reservas_credito.xlsx
+++ b/datos-referencia/reservas_credito.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,27 +429,570 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>fecha</t>
+          <t>fecha_emision</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>importe</t>
+          <t>fecha_entrada</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>fecha_salida</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>habitaciones</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>noches</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>tarifa_noche</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>estado</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>dias</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>vencido</t>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>RES-2026-0401</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Telefonica España SAU</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>320</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3200</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>PENDIENTE_FACTURA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>RES-2026-0402</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Repsol Comercial de Productos</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>200</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1600</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>PENDIENTE_FACTURA</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>RES-2026-0403</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Viajes El Corte Inglés</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>8</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" t="n">
+        <v>210</v>
+      </c>
+      <c r="I4" t="n">
+        <v>6720</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>FACTURADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>RES-2026-0404</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Accenture SLU</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>237</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2370</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>PENDIENTE_FACTURA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RES-2026-0405</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Deloitte Advisory SL</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>200</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4000</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>FACTURADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RES-2026-0406</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Barceló Viajes SL</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" t="n">
+        <v>7</v>
+      </c>
+      <c r="H7" t="n">
+        <v>151.43</v>
+      </c>
+      <c r="I7" t="n">
+        <v>10600</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>FACTURADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>RES-2026-0407</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>KPMG Asesores SL</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>185</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1480</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>PENDIENTE_FACTURA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>RES-2026-0408</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Telefonica España SAU</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" t="n">
+        <v>323.33</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4850</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>FACTURADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>RES-2026-0409</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>McKinsey &amp; Company</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>220</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2200</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>PENDIENTE_FACTURA</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>RES-2026-0410</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Viajes El Corte Inglés</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>247.5</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4950</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>FACTURADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>RES-2026-0411</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Accenture SLU</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" t="n">
+        <v>215</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2580</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>COBRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>RES-2026-0412</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Deloitte Advisory SL</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>240</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1440</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>COBRADO</t>
         </is>
       </c>
     </row>

--- a/datos-referencia/reservas_credito.xlsx
+++ b/datos-referencia/reservas_credito.xlsx
@@ -37,13 +37,13 @@
     <t>noches</t>
   </si>
   <si>
-    <t>tarifa_noche</t>
-  </si>
-  <si>
-    <t>total</t>
+    <t>importe</t>
   </si>
   <si>
     <t>estado</t>
+  </si>
+  <si>
+    <t>hotel</t>
   </si>
 </sst>
 </file>
